--- a/reports/pdf_change_20260720.xlsx
+++ b/reports/pdf_change_20260720.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,11 +35,6 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -63,6 +58,15 @@
       <b val="1"/>
       <color rgb="000070C0"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -70,11 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -99,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -139,19 +143,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -160,17 +170,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,21 +560,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>코스닥 액티브 ETF PDF 변화   ·   당일 2026-07-20  vs  전영업일 2026-07-17</t>
+          <t>코스닥 액티브 ETF PDF 변화   ·   당일 2026-07-20  vs  전영업일 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 1/7  ·  대기: KoAct, KoAct, TIME, TIME, PLUS, TIGER</t>
+          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 76억(1.7%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -583,44 +588,154 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>920040000</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>1.71%→1.99%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>148→165</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-414559200</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>3.79%→3.46%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>422→411</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-2103103200</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>10.22%→9.52%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>234→223</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 11억(0.3%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -634,232 +749,82 @@
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 26억(1.0%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 25억(1.0%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 4억(0.8%)      당일 2026-07-20  vs  전영업일 2026-07-17      매수 2종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>570998400</v>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>7.10%→8.37%</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>187→215</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>코오롱티슈진</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>-244922400</v>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>3.32%→2.24%</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>197→163</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>파마리서치</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>702612000</v>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>3.26%→4.77%</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>46→64</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>에이비엘바이오</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>-32</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>-280627200</v>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>7.08%→6.38%</t>
-        </is>
-      </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>413→381</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="n"/>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>-264642400</v>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>8.62%→7.74%</t>
-        </is>
-      </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>359→337</t>
-        </is>
-      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="20" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 4억(0.8%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -873,19 +838,229 @@
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>570998400</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>7.10%→8.37%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>187→215</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>코오롱티슈진</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-244922400</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>3.32%→2.24%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>197→163</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>702612000</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>3.26%→4.77%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>46→64</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-280627200</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>7.08%→6.38%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>413→381</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-264642400</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>8.62%→7.74%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>359→337</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="16">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A15:K15"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A10:K10"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A9:K9"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260720.xlsx
+++ b/reports/pdf_change_20260720.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 76억(1.7%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,592억   ·   현금 76억(1.7%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>920040000</v>
+        <v>927520000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-414559200</v>
+        <v>-2120201600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>3.79%→3.46%</t>
+          <t>10.22%→9.52%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>422→411</t>
+          <t>234→223</t>
         </is>
       </c>
     </row>
@@ -712,30 +712,30 @@
       <c r="E7" s="17" t="n"/>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2103103200</v>
+        <v>-417929600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>10.22%→9.52%</t>
+          <t>3.79%→3.46%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>234→223</t>
+          <t>422→411</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 11억(0.3%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,085억   ·   현금 11억(0.3%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -759,7 +759,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,884억   ·   현금 26억(1.0%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 26억(1.0%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -783,7 +783,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,500억   ·   현금 25억(1.0%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,453억   ·   현금 25억(1.0%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -805,258 +805,536 @@
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="20" t="n"/>
-      <c r="H18" s="20" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="20" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 4억(0.8%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 2종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 2억(100.0%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 5종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>39404300</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>0.28%→0.40%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>63→89</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-61138800</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.97%→0.79%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>574→466</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>39644000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>2.84%→2.96%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>528→550</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-73</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-91461700</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>1.58%→1.31%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>422→349</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>570998400</v>
+        <v>94248000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>7.10%→8.37%</t>
+          <t>2.05%→2.33%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>187→215</t>
+          <t>131→149</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>코오롱티슈진</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-34</v>
+        <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-244922400</v>
+        <v>-69666000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>3.32%→2.24%</t>
+          <t>0.31%→0.10%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>197→163</t>
+          <t>9→3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>35904000</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>0.98%→1.09%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>55→61</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-69190000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>1.49%→1.28%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>36→31</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>54774000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1.99%→2.15%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>73→79</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 528억   ·   현금 4억(0.8%)      당일 2026-07-20  vs  전영업일 2026-07-16      매수 2종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>570998400</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>7.10%→8.37%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>187→215</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>코오롱티슈진</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-244922400</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>3.32%→2.24%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>197→163</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B31" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C31" s="11" t="n">
         <v>702612000</v>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>3.26%→4.77%</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>46→64</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H31" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I24" s="15" t="n">
+      <c r="I31" s="15" t="n">
         <v>-280627200</v>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>7.08%→6.38%</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>413→381</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="17" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H32" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I25" s="15" t="n">
+      <c r="I32" s="15" t="n">
         <v>-264642400</v>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>8.62%→7.74%</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>359→337</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="20" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A21:E21"/>
+  <mergeCells count="18">
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="G21:K21"/>
     <mergeCell ref="A27:K27"/>
     <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
+    <mergeCell ref="G28:K28"/>
     <mergeCell ref="A10:K10"/>
+    <mergeCell ref="G19:K19"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A9:K9"/>

--- a/reports/pdf_change_20260720.xlsx
+++ b/reports/pdf_change_20260720.xlsx
@@ -1028,23 +1028,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>35904000</v>
+        <v>54774000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.09%</t>
+          <t>1.99%→2.15%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>55→61</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1072,23 +1072,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>54774000</v>
+        <v>35904000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.15%</t>
+          <t>0.98%→1.09%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>55→61</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>

--- a/reports/pdf_change_20260720.xlsx
+++ b/reports/pdf_change_20260720.xlsx
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2120201600</v>
+        <v>-417929600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>10.22%→9.52%</t>
+          <t>3.79%→3.46%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>234→223</t>
+          <t>422→411</t>
         </is>
       </c>
     </row>
@@ -712,23 +712,23 @@
       <c r="E7" s="17" t="n"/>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-417929600</v>
+        <v>-2120201600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>3.79%→3.46%</t>
+          <t>10.22%→9.52%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>422→411</t>
+          <t>234→223</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260720.xlsx
+++ b/reports/pdf_change_20260720.xlsx
@@ -1028,23 +1028,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>54774000</v>
+        <v>35904000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.15%</t>
+          <t>0.98%→1.09%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>55→61</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1072,23 +1072,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>35904000</v>
+        <v>54774000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.09%</t>
+          <t>1.99%→2.15%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>55→61</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>

--- a/reports/pdf_change_20260720.xlsx
+++ b/reports/pdf_change_20260720.xlsx
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-417929600</v>
+        <v>-2120201600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>3.79%→3.46%</t>
+          <t>10.22%→9.52%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>422→411</t>
+          <t>234→223</t>
         </is>
       </c>
     </row>
@@ -712,23 +712,23 @@
       <c r="E7" s="17" t="n"/>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2120201600</v>
+        <v>-417929600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>10.22%→9.52%</t>
+          <t>3.79%→3.46%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>234→223</t>
+          <t>422→411</t>
         </is>
       </c>
     </row>
